--- a/ministry/2027_사역명단_올리기_양식.xlsx
+++ b/ministry/2027_사역명단_올리기_양식.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>김세웅</t>
+          <t>홍길동</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>안수집사</t>
+          <t>집사</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>앱 로그인과 똑같이 — 한 글자만 달라도 다른 분이 됩니다   예) 김세웅</t>
+          <t>앱 로그인과 똑같이 — 한 글자만 달라도 다른 분이 됩니다   예) 홍길동</t>
         </is>
       </c>
     </row>

--- a/ministry/2027_사역명단_올리기_양식.xlsx
+++ b/ministry/2027_사역명단_올리기_양식.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,15 +30,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="009AA3B2"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00A33A3A"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -90,21 +81,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -475,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -486,6 +470,10 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -529,1018 +517,1529 @@
           <t>하위 선택(선택)</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>신청일(선택)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>임명일(선택)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>상태(선택)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>사유(취소일 때)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>화평</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>집사</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>010-1234-5678</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>신앙운동</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>제자양육부</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>사랑</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>권사</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>010-2345-6789</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>방송실 운영</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>방송전산부</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>믿음</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>박철수</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>집사</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>010-3456-7890</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>새가족부</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>↑ 위 세 줄은 예시입니다. 지우고 적어 주세요. (머리글 줄은 그대로 복사하셔도 됩니다)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="E6" s="5" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="E8" s="5" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="E10" s="5" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="E12" s="5" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="E14" s="5" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="E16" s="5" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="E19" s="5" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="E21" s="5" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="E23" s="5" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="E27" s="5" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="E29" s="5" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="E31" s="5" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="E32" s="5" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="E33" s="5" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="E34" s="5" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="E35" s="5" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="E36" s="5" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="E38" s="5" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="E40" s="5" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="E41" s="5" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="E42" s="5" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="E43" s="5" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="E44" s="5" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="E45" s="5" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="E47" s="5" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="E49" s="5" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="E50" s="5" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="E51" s="5" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="E52" s="5" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="E53" s="5" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="E54" s="5" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="E55" s="5" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="E56" s="5" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="E57" s="5" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
     </row>
     <row r="58">
-      <c r="E58" s="5" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="E59" s="5" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="E60" s="5" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
     </row>
     <row r="61">
-      <c r="E61" s="5" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="E62" s="5" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="E63" s="5" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
     </row>
     <row r="64">
-      <c r="E64" s="5" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="E65" s="5" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="E66" s="5" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
     </row>
     <row r="67">
-      <c r="E67" s="5" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
     </row>
     <row r="68">
-      <c r="E68" s="5" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="E69" s="5" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
     </row>
     <row r="70">
-      <c r="E70" s="5" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
     </row>
     <row r="71">
-      <c r="E71" s="5" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
     </row>
     <row r="72">
-      <c r="E72" s="5" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
     </row>
     <row r="73">
-      <c r="E73" s="5" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
     </row>
     <row r="74">
-      <c r="E74" s="5" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="E75" s="5" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
     </row>
     <row r="76">
-      <c r="E76" s="5" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
     </row>
     <row r="77">
-      <c r="E77" s="5" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
     </row>
     <row r="78">
-      <c r="E78" s="5" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="E79" s="5" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
     </row>
     <row r="80">
-      <c r="E80" s="5" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
     </row>
     <row r="81">
-      <c r="E81" s="5" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="E82" s="5" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
     </row>
     <row r="83">
-      <c r="E83" s="5" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
     </row>
     <row r="84">
-      <c r="E84" s="5" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
     </row>
     <row r="85">
-      <c r="E85" s="5" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
     </row>
     <row r="86">
-      <c r="E86" s="5" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
     </row>
     <row r="87">
-      <c r="E87" s="5" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
     </row>
     <row r="88">
-      <c r="E88" s="5" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
     </row>
     <row r="89">
-      <c r="E89" s="5" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
     </row>
     <row r="90">
-      <c r="E90" s="5" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n"/>
     </row>
     <row r="91">
-      <c r="E91" s="5" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n"/>
     </row>
     <row r="92">
-      <c r="E92" s="5" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
     </row>
     <row r="93">
-      <c r="E93" s="5" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
     </row>
     <row r="94">
-      <c r="E94" s="5" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
     </row>
     <row r="95">
-      <c r="E95" s="5" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
     </row>
     <row r="96">
-      <c r="E96" s="5" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
     </row>
     <row r="97">
-      <c r="E97" s="5" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
     </row>
     <row r="98">
-      <c r="E98" s="5" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
     </row>
     <row r="99">
-      <c r="E99" s="5" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n"/>
     </row>
     <row r="100">
-      <c r="E100" s="5" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
     </row>
     <row r="101">
-      <c r="E101" s="5" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
     </row>
     <row r="102">
-      <c r="E102" s="5" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
     </row>
     <row r="103">
-      <c r="E103" s="5" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
     </row>
     <row r="104">
-      <c r="E104" s="5" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
     </row>
     <row r="105">
-      <c r="E105" s="5" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n"/>
     </row>
     <row r="106">
-      <c r="E106" s="5" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
     </row>
     <row r="107">
-      <c r="E107" s="5" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
     </row>
     <row r="108">
-      <c r="E108" s="5" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="E109" s="5" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
     </row>
     <row r="110">
-      <c r="E110" s="5" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="E111" s="5" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="I111" s="2" t="n"/>
+      <c r="J111" s="2" t="n"/>
     </row>
     <row r="112">
-      <c r="E112" s="5" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="E113" s="5" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
     </row>
     <row r="114">
-      <c r="E114" s="5" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
     </row>
     <row r="115">
-      <c r="E115" s="5" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="n"/>
     </row>
     <row r="116">
-      <c r="E116" s="5" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
     </row>
     <row r="117">
-      <c r="E117" s="5" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
+      <c r="J117" s="2" t="n"/>
     </row>
     <row r="118">
-      <c r="E118" s="5" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
     </row>
     <row r="119">
-      <c r="E119" s="5" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
     </row>
     <row r="120">
-      <c r="E120" s="5" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n"/>
     </row>
     <row r="121">
-      <c r="E121" s="5" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="n"/>
     </row>
     <row r="122">
-      <c r="E122" s="5" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n"/>
     </row>
     <row r="123">
-      <c r="E123" s="5" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="n"/>
     </row>
     <row r="124">
-      <c r="E124" s="5" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
     </row>
     <row r="125">
-      <c r="E125" s="5" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="I125" s="2" t="n"/>
+      <c r="J125" s="2" t="n"/>
     </row>
     <row r="126">
-      <c r="E126" s="5" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
     </row>
     <row r="127">
-      <c r="E127" s="5" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="n"/>
     </row>
     <row r="128">
-      <c r="E128" s="5" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="n"/>
     </row>
     <row r="129">
-      <c r="E129" s="5" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="n"/>
     </row>
     <row r="130">
-      <c r="E130" s="5" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
     </row>
     <row r="131">
-      <c r="E131" s="5" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
     </row>
     <row r="132">
-      <c r="E132" s="5" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
     </row>
     <row r="133">
-      <c r="E133" s="5" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+      <c r="J133" s="2" t="n"/>
     </row>
     <row r="134">
-      <c r="E134" s="5" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
     </row>
     <row r="135">
-      <c r="E135" s="5" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
     </row>
     <row r="136">
-      <c r="E136" s="5" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="I136" s="2" t="n"/>
+      <c r="J136" s="2" t="n"/>
     </row>
     <row r="137">
-      <c r="E137" s="5" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="I137" s="2" t="n"/>
+      <c r="J137" s="2" t="n"/>
     </row>
     <row r="138">
-      <c r="E138" s="5" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
     </row>
     <row r="139">
-      <c r="E139" s="5" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="n"/>
     </row>
     <row r="140">
-      <c r="E140" s="5" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
+      <c r="J140" s="2" t="n"/>
     </row>
     <row r="141">
-      <c r="E141" s="5" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="I141" s="2" t="n"/>
+      <c r="J141" s="2" t="n"/>
     </row>
     <row r="142">
-      <c r="E142" s="5" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
     </row>
     <row r="143">
-      <c r="E143" s="5" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
+      <c r="J143" s="2" t="n"/>
     </row>
     <row r="144">
-      <c r="E144" s="5" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
     </row>
     <row r="145">
-      <c r="E145" s="5" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
     </row>
     <row r="146">
-      <c r="E146" s="5" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
     </row>
     <row r="147">
-      <c r="E147" s="5" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="I147" s="2" t="n"/>
+      <c r="J147" s="2" t="n"/>
     </row>
     <row r="148">
-      <c r="E148" s="5" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
     </row>
     <row r="149">
-      <c r="E149" s="5" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="n"/>
     </row>
     <row r="150">
-      <c r="E150" s="5" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
     </row>
     <row r="151">
-      <c r="E151" s="5" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="I151" s="2" t="n"/>
+      <c r="J151" s="2" t="n"/>
     </row>
     <row r="152">
-      <c r="E152" s="5" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
     </row>
     <row r="153">
-      <c r="E153" s="5" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
+      <c r="J153" s="2" t="n"/>
     </row>
     <row r="154">
-      <c r="E154" s="5" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
     </row>
     <row r="155">
-      <c r="E155" s="5" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="I155" s="2" t="n"/>
+      <c r="J155" s="2" t="n"/>
     </row>
     <row r="156">
-      <c r="E156" s="5" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
     </row>
     <row r="157">
-      <c r="E157" s="5" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="I157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
     </row>
     <row r="158">
-      <c r="E158" s="5" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
     </row>
     <row r="159">
-      <c r="E159" s="5" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
+      <c r="J159" s="2" t="n"/>
     </row>
     <row r="160">
-      <c r="E160" s="5" t="n"/>
+      <c r="E160" s="2" t="n"/>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="n"/>
     </row>
     <row r="161">
-      <c r="E161" s="5" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
+      <c r="J161" s="2" t="n"/>
     </row>
     <row r="162">
-      <c r="E162" s="5" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="n"/>
     </row>
     <row r="163">
-      <c r="E163" s="5" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="I163" s="2" t="n"/>
+      <c r="J163" s="2" t="n"/>
     </row>
     <row r="164">
-      <c r="E164" s="5" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="I164" s="2" t="n"/>
+      <c r="J164" s="2" t="n"/>
     </row>
     <row r="165">
-      <c r="E165" s="5" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="n"/>
     </row>
     <row r="166">
-      <c r="E166" s="5" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="n"/>
     </row>
     <row r="167">
-      <c r="E167" s="5" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="n"/>
     </row>
     <row r="168">
-      <c r="E168" s="5" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
     </row>
     <row r="169">
-      <c r="E169" s="5" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
     </row>
     <row r="170">
-      <c r="E170" s="5" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
     </row>
     <row r="171">
-      <c r="E171" s="5" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="I171" s="2" t="n"/>
+      <c r="J171" s="2" t="n"/>
     </row>
     <row r="172">
-      <c r="E172" s="5" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="n"/>
     </row>
     <row r="173">
-      <c r="E173" s="5" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="I173" s="2" t="n"/>
+      <c r="J173" s="2" t="n"/>
     </row>
     <row r="174">
-      <c r="E174" s="5" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="I174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
     </row>
     <row r="175">
-      <c r="E175" s="5" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="I175" s="2" t="n"/>
+      <c r="J175" s="2" t="n"/>
     </row>
     <row r="176">
-      <c r="E176" s="5" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="n"/>
     </row>
     <row r="177">
-      <c r="E177" s="5" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="I177" s="2" t="n"/>
+      <c r="J177" s="2" t="n"/>
     </row>
     <row r="178">
-      <c r="E178" s="5" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
     </row>
     <row r="179">
-      <c r="E179" s="5" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="n"/>
     </row>
     <row r="180">
-      <c r="E180" s="5" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
     </row>
     <row r="181">
-      <c r="E181" s="5" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="n"/>
     </row>
     <row r="182">
-      <c r="E182" s="5" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
     </row>
     <row r="183">
-      <c r="E183" s="5" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+      <c r="J183" s="2" t="n"/>
     </row>
     <row r="184">
-      <c r="E184" s="5" t="n"/>
+      <c r="E184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="n"/>
     </row>
     <row r="185">
-      <c r="E185" s="5" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="I185" s="2" t="n"/>
+      <c r="J185" s="2" t="n"/>
     </row>
     <row r="186">
-      <c r="E186" s="5" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+      <c r="J186" s="2" t="n"/>
     </row>
     <row r="187">
-      <c r="E187" s="5" t="n"/>
+      <c r="E187" s="2" t="n"/>
+      <c r="I187" s="2" t="n"/>
+      <c r="J187" s="2" t="n"/>
     </row>
     <row r="188">
-      <c r="E188" s="5" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="I188" s="2" t="n"/>
+      <c r="J188" s="2" t="n"/>
     </row>
     <row r="189">
-      <c r="E189" s="5" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="I189" s="2" t="n"/>
+      <c r="J189" s="2" t="n"/>
     </row>
     <row r="190">
-      <c r="E190" s="5" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="I190" s="2" t="n"/>
+      <c r="J190" s="2" t="n"/>
     </row>
     <row r="191">
-      <c r="E191" s="5" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="I191" s="2" t="n"/>
+      <c r="J191" s="2" t="n"/>
     </row>
     <row r="192">
-      <c r="E192" s="5" t="n"/>
+      <c r="E192" s="2" t="n"/>
+      <c r="I192" s="2" t="n"/>
+      <c r="J192" s="2" t="n"/>
     </row>
     <row r="193">
-      <c r="E193" s="5" t="n"/>
+      <c r="E193" s="2" t="n"/>
+      <c r="I193" s="2" t="n"/>
+      <c r="J193" s="2" t="n"/>
     </row>
     <row r="194">
-      <c r="E194" s="5" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="I194" s="2" t="n"/>
+      <c r="J194" s="2" t="n"/>
     </row>
     <row r="195">
-      <c r="E195" s="5" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="I195" s="2" t="n"/>
+      <c r="J195" s="2" t="n"/>
     </row>
     <row r="196">
-      <c r="E196" s="5" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="n"/>
     </row>
     <row r="197">
-      <c r="E197" s="5" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
+      <c r="J197" s="2" t="n"/>
     </row>
     <row r="198">
-      <c r="E198" s="5" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+      <c r="J198" s="2" t="n"/>
     </row>
     <row r="199">
-      <c r="E199" s="5" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
     </row>
     <row r="200">
-      <c r="E200" s="5" t="n"/>
+      <c r="E200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+      <c r="J200" s="2" t="n"/>
     </row>
     <row r="201">
-      <c r="E201" s="5" t="n"/>
+      <c r="E201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
     </row>
     <row r="202">
-      <c r="E202" s="5" t="n"/>
+      <c r="E202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
     </row>
     <row r="203">
-      <c r="E203" s="5" t="n"/>
+      <c r="E203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+      <c r="J203" s="2" t="n"/>
     </row>
     <row r="204">
-      <c r="E204" s="5" t="n"/>
+      <c r="E204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
     </row>
     <row r="205">
-      <c r="E205" s="5" t="n"/>
+      <c r="E205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
+      <c r="J205" s="2" t="n"/>
     </row>
     <row r="206">
-      <c r="E206" s="5" t="n"/>
+      <c r="E206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="n"/>
     </row>
     <row r="207">
-      <c r="E207" s="5" t="n"/>
+      <c r="E207" s="2" t="n"/>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="n"/>
     </row>
     <row r="208">
-      <c r="E208" s="5" t="n"/>
+      <c r="E208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
     </row>
     <row r="209">
-      <c r="E209" s="5" t="n"/>
+      <c r="E209" s="2" t="n"/>
+      <c r="I209" s="2" t="n"/>
+      <c r="J209" s="2" t="n"/>
     </row>
     <row r="210">
-      <c r="E210" s="5" t="n"/>
+      <c r="E210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="n"/>
     </row>
     <row r="211">
-      <c r="E211" s="5" t="n"/>
+      <c r="E211" s="2" t="n"/>
+      <c r="I211" s="2" t="n"/>
+      <c r="J211" s="2" t="n"/>
     </row>
     <row r="212">
-      <c r="E212" s="5" t="n"/>
+      <c r="E212" s="2" t="n"/>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="n"/>
     </row>
     <row r="213">
-      <c r="E213" s="5" t="n"/>
+      <c r="E213" s="2" t="n"/>
+      <c r="I213" s="2" t="n"/>
+      <c r="J213" s="2" t="n"/>
     </row>
     <row r="214">
-      <c r="E214" s="5" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
     </row>
     <row r="215">
-      <c r="E215" s="5" t="n"/>
+      <c r="E215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
+      <c r="J215" s="2" t="n"/>
     </row>
     <row r="216">
-      <c r="E216" s="5" t="n"/>
+      <c r="E216" s="2" t="n"/>
+      <c r="I216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
     </row>
     <row r="217">
-      <c r="E217" s="5" t="n"/>
+      <c r="E217" s="2" t="n"/>
+      <c r="I217" s="2" t="n"/>
+      <c r="J217" s="2" t="n"/>
     </row>
     <row r="218">
-      <c r="E218" s="5" t="n"/>
+      <c r="E218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
+      <c r="J218" s="2" t="n"/>
     </row>
     <row r="219">
-      <c r="E219" s="5" t="n"/>
+      <c r="E219" s="2" t="n"/>
+      <c r="I219" s="2" t="n"/>
+      <c r="J219" s="2" t="n"/>
     </row>
     <row r="220">
-      <c r="E220" s="5" t="n"/>
+      <c r="E220" s="2" t="n"/>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
     </row>
     <row r="221">
-      <c r="E221" s="5" t="n"/>
+      <c r="E221" s="2" t="n"/>
+      <c r="I221" s="2" t="n"/>
+      <c r="J221" s="2" t="n"/>
     </row>
     <row r="222">
-      <c r="E222" s="5" t="n"/>
+      <c r="E222" s="2" t="n"/>
+      <c r="I222" s="2" t="n"/>
+      <c r="J222" s="2" t="n"/>
     </row>
     <row r="223">
-      <c r="E223" s="5" t="n"/>
+      <c r="E223" s="2" t="n"/>
+      <c r="I223" s="2" t="n"/>
+      <c r="J223" s="2" t="n"/>
     </row>
     <row r="224">
-      <c r="E224" s="5" t="n"/>
+      <c r="E224" s="2" t="n"/>
+      <c r="I224" s="2" t="n"/>
+      <c r="J224" s="2" t="n"/>
     </row>
     <row r="225">
-      <c r="E225" s="5" t="n"/>
+      <c r="E225" s="2" t="n"/>
+      <c r="I225" s="2" t="n"/>
+      <c r="J225" s="2" t="n"/>
     </row>
     <row r="226">
-      <c r="E226" s="5" t="n"/>
+      <c r="E226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+      <c r="J226" s="2" t="n"/>
     </row>
     <row r="227">
-      <c r="E227" s="5" t="n"/>
+      <c r="E227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+      <c r="J227" s="2" t="n"/>
     </row>
     <row r="228">
-      <c r="E228" s="5" t="n"/>
+      <c r="E228" s="2" t="n"/>
+      <c r="I228" s="2" t="n"/>
+      <c r="J228" s="2" t="n"/>
     </row>
     <row r="229">
-      <c r="E229" s="5" t="n"/>
+      <c r="E229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+      <c r="J229" s="2" t="n"/>
     </row>
     <row r="230">
-      <c r="E230" s="5" t="n"/>
+      <c r="E230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+      <c r="J230" s="2" t="n"/>
     </row>
     <row r="231">
-      <c r="E231" s="5" t="n"/>
+      <c r="E231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
     </row>
     <row r="232">
-      <c r="E232" s="5" t="n"/>
+      <c r="E232" s="2" t="n"/>
+      <c r="I232" s="2" t="n"/>
+      <c r="J232" s="2" t="n"/>
     </row>
     <row r="233">
-      <c r="E233" s="5" t="n"/>
+      <c r="E233" s="2" t="n"/>
+      <c r="I233" s="2" t="n"/>
+      <c r="J233" s="2" t="n"/>
     </row>
     <row r="234">
-      <c r="E234" s="5" t="n"/>
+      <c r="E234" s="2" t="n"/>
+      <c r="I234" s="2" t="n"/>
+      <c r="J234" s="2" t="n"/>
     </row>
     <row r="235">
-      <c r="E235" s="5" t="n"/>
+      <c r="E235" s="2" t="n"/>
+      <c r="I235" s="2" t="n"/>
+      <c r="J235" s="2" t="n"/>
     </row>
     <row r="236">
-      <c r="E236" s="5" t="n"/>
+      <c r="E236" s="2" t="n"/>
+      <c r="I236" s="2" t="n"/>
+      <c r="J236" s="2" t="n"/>
     </row>
     <row r="237">
-      <c r="E237" s="5" t="n"/>
+      <c r="E237" s="2" t="n"/>
+      <c r="I237" s="2" t="n"/>
+      <c r="J237" s="2" t="n"/>
     </row>
     <row r="238">
-      <c r="E238" s="5" t="n"/>
+      <c r="E238" s="2" t="n"/>
+      <c r="I238" s="2" t="n"/>
+      <c r="J238" s="2" t="n"/>
     </row>
     <row r="239">
-      <c r="E239" s="5" t="n"/>
+      <c r="E239" s="2" t="n"/>
+      <c r="I239" s="2" t="n"/>
+      <c r="J239" s="2" t="n"/>
     </row>
     <row r="240">
-      <c r="E240" s="5" t="n"/>
+      <c r="E240" s="2" t="n"/>
+      <c r="I240" s="2" t="n"/>
+      <c r="J240" s="2" t="n"/>
     </row>
     <row r="241">
-      <c r="E241" s="5" t="n"/>
+      <c r="E241" s="2" t="n"/>
+      <c r="I241" s="2" t="n"/>
+      <c r="J241" s="2" t="n"/>
     </row>
     <row r="242">
-      <c r="E242" s="5" t="n"/>
+      <c r="E242" s="2" t="n"/>
+      <c r="I242" s="2" t="n"/>
+      <c r="J242" s="2" t="n"/>
     </row>
     <row r="243">
-      <c r="E243" s="5" t="n"/>
+      <c r="E243" s="2" t="n"/>
+      <c r="I243" s="2" t="n"/>
+      <c r="J243" s="2" t="n"/>
     </row>
     <row r="244">
-      <c r="E244" s="5" t="n"/>
+      <c r="E244" s="2" t="n"/>
+      <c r="I244" s="2" t="n"/>
+      <c r="J244" s="2" t="n"/>
     </row>
     <row r="245">
-      <c r="E245" s="5" t="n"/>
+      <c r="E245" s="2" t="n"/>
+      <c r="I245" s="2" t="n"/>
+      <c r="J245" s="2" t="n"/>
     </row>
     <row r="246">
-      <c r="E246" s="5" t="n"/>
+      <c r="E246" s="2" t="n"/>
+      <c r="I246" s="2" t="n"/>
+      <c r="J246" s="2" t="n"/>
     </row>
     <row r="247">
-      <c r="E247" s="5" t="n"/>
+      <c r="E247" s="2" t="n"/>
+      <c r="I247" s="2" t="n"/>
+      <c r="J247" s="2" t="n"/>
     </row>
     <row r="248">
-      <c r="E248" s="5" t="n"/>
+      <c r="E248" s="2" t="n"/>
+      <c r="I248" s="2" t="n"/>
+      <c r="J248" s="2" t="n"/>
     </row>
     <row r="249">
-      <c r="E249" s="5" t="n"/>
+      <c r="E249" s="2" t="n"/>
+      <c r="I249" s="2" t="n"/>
+      <c r="J249" s="2" t="n"/>
     </row>
     <row r="250">
-      <c r="E250" s="5" t="n"/>
+      <c r="E250" s="2" t="n"/>
+      <c r="I250" s="2" t="n"/>
+      <c r="J250" s="2" t="n"/>
     </row>
     <row r="251">
-      <c r="E251" s="5" t="n"/>
+      <c r="E251" s="2" t="n"/>
+      <c r="I251" s="2" t="n"/>
+      <c r="J251" s="2" t="n"/>
     </row>
     <row r="252">
-      <c r="E252" s="5" t="n"/>
+      <c r="E252" s="2" t="n"/>
+      <c r="I252" s="2" t="n"/>
+      <c r="J252" s="2" t="n"/>
     </row>
     <row r="253">
-      <c r="E253" s="5" t="n"/>
+      <c r="E253" s="2" t="n"/>
+      <c r="I253" s="2" t="n"/>
+      <c r="J253" s="2" t="n"/>
     </row>
     <row r="254">
-      <c r="E254" s="5" t="n"/>
+      <c r="E254" s="2" t="n"/>
+      <c r="I254" s="2" t="n"/>
+      <c r="J254" s="2" t="n"/>
     </row>
     <row r="255">
-      <c r="E255" s="5" t="n"/>
+      <c r="E255" s="2" t="n"/>
+      <c r="I255" s="2" t="n"/>
+      <c r="J255" s="2" t="n"/>
     </row>
     <row r="256">
-      <c r="E256" s="5" t="n"/>
+      <c r="E256" s="2" t="n"/>
+      <c r="I256" s="2" t="n"/>
+      <c r="J256" s="2" t="n"/>
     </row>
     <row r="257">
-      <c r="E257" s="5" t="n"/>
+      <c r="E257" s="2" t="n"/>
+      <c r="I257" s="2" t="n"/>
+      <c r="J257" s="2" t="n"/>
     </row>
     <row r="258">
-      <c r="E258" s="5" t="n"/>
+      <c r="E258" s="2" t="n"/>
+      <c r="I258" s="2" t="n"/>
+      <c r="J258" s="2" t="n"/>
     </row>
     <row r="259">
-      <c r="E259" s="5" t="n"/>
+      <c r="E259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="n"/>
     </row>
     <row r="260">
-      <c r="E260" s="5" t="n"/>
+      <c r="E260" s="2" t="n"/>
+      <c r="I260" s="2" t="n"/>
+      <c r="J260" s="2" t="n"/>
     </row>
     <row r="261">
-      <c r="E261" s="5" t="n"/>
+      <c r="E261" s="2" t="n"/>
+      <c r="I261" s="2" t="n"/>
+      <c r="J261" s="2" t="n"/>
     </row>
     <row r="262">
-      <c r="E262" s="5" t="n"/>
+      <c r="E262" s="2" t="n"/>
+      <c r="I262" s="2" t="n"/>
+      <c r="J262" s="2" t="n"/>
     </row>
     <row r="263">
-      <c r="E263" s="5" t="n"/>
+      <c r="E263" s="2" t="n"/>
+      <c r="I263" s="2" t="n"/>
+      <c r="J263" s="2" t="n"/>
     </row>
     <row r="264">
-      <c r="E264" s="5" t="n"/>
+      <c r="E264" s="2" t="n"/>
+      <c r="I264" s="2" t="n"/>
+      <c r="J264" s="2" t="n"/>
     </row>
     <row r="265">
-      <c r="E265" s="5" t="n"/>
+      <c r="E265" s="2" t="n"/>
+      <c r="I265" s="2" t="n"/>
+      <c r="J265" s="2" t="n"/>
     </row>
     <row r="266">
-      <c r="E266" s="5" t="n"/>
+      <c r="E266" s="2" t="n"/>
+      <c r="I266" s="2" t="n"/>
+      <c r="J266" s="2" t="n"/>
     </row>
     <row r="267">
-      <c r="E267" s="5" t="n"/>
+      <c r="E267" s="2" t="n"/>
+      <c r="I267" s="2" t="n"/>
+      <c r="J267" s="2" t="n"/>
     </row>
     <row r="268">
-      <c r="E268" s="5" t="n"/>
+      <c r="E268" s="2" t="n"/>
+      <c r="I268" s="2" t="n"/>
+      <c r="J268" s="2" t="n"/>
     </row>
     <row r="269">
-      <c r="E269" s="5" t="n"/>
+      <c r="E269" s="2" t="n"/>
+      <c r="I269" s="2" t="n"/>
+      <c r="J269" s="2" t="n"/>
     </row>
     <row r="270">
-      <c r="E270" s="5" t="n"/>
+      <c r="E270" s="2" t="n"/>
+      <c r="I270" s="2" t="n"/>
+      <c r="J270" s="2" t="n"/>
     </row>
     <row r="271">
-      <c r="E271" s="5" t="n"/>
+      <c r="E271" s="2" t="n"/>
+      <c r="I271" s="2" t="n"/>
+      <c r="J271" s="2" t="n"/>
     </row>
     <row r="272">
-      <c r="E272" s="5" t="n"/>
+      <c r="E272" s="2" t="n"/>
+      <c r="I272" s="2" t="n"/>
+      <c r="J272" s="2" t="n"/>
     </row>
     <row r="273">
-      <c r="E273" s="5" t="n"/>
+      <c r="E273" s="2" t="n"/>
+      <c r="I273" s="2" t="n"/>
+      <c r="J273" s="2" t="n"/>
     </row>
     <row r="274">
-      <c r="E274" s="5" t="n"/>
+      <c r="E274" s="2" t="n"/>
+      <c r="I274" s="2" t="n"/>
+      <c r="J274" s="2" t="n"/>
     </row>
     <row r="275">
-      <c r="E275" s="5" t="n"/>
+      <c r="E275" s="2" t="n"/>
+      <c r="I275" s="2" t="n"/>
+      <c r="J275" s="2" t="n"/>
     </row>
     <row r="276">
-      <c r="E276" s="5" t="n"/>
+      <c r="E276" s="2" t="n"/>
+      <c r="I276" s="2" t="n"/>
+      <c r="J276" s="2" t="n"/>
     </row>
     <row r="277">
-      <c r="E277" s="5" t="n"/>
+      <c r="E277" s="2" t="n"/>
+      <c r="I277" s="2" t="n"/>
+      <c r="J277" s="2" t="n"/>
     </row>
     <row r="278">
-      <c r="E278" s="5" t="n"/>
+      <c r="E278" s="2" t="n"/>
+      <c r="I278" s="2" t="n"/>
+      <c r="J278" s="2" t="n"/>
     </row>
     <row r="279">
-      <c r="E279" s="5" t="n"/>
+      <c r="E279" s="2" t="n"/>
+      <c r="I279" s="2" t="n"/>
+      <c r="J279" s="2" t="n"/>
     </row>
     <row r="280">
-      <c r="E280" s="5" t="n"/>
+      <c r="E280" s="2" t="n"/>
+      <c r="I280" s="2" t="n"/>
+      <c r="J280" s="2" t="n"/>
     </row>
     <row r="281">
-      <c r="E281" s="5" t="n"/>
+      <c r="E281" s="2" t="n"/>
+      <c r="I281" s="2" t="n"/>
+      <c r="J281" s="2" t="n"/>
     </row>
     <row r="282">
-      <c r="E282" s="5" t="n"/>
+      <c r="E282" s="2" t="n"/>
+      <c r="I282" s="2" t="n"/>
+      <c r="J282" s="2" t="n"/>
     </row>
     <row r="283">
-      <c r="E283" s="5" t="n"/>
+      <c r="E283" s="2" t="n"/>
+      <c r="I283" s="2" t="n"/>
+      <c r="J283" s="2" t="n"/>
     </row>
     <row r="284">
-      <c r="E284" s="5" t="n"/>
+      <c r="E284" s="2" t="n"/>
+      <c r="I284" s="2" t="n"/>
+      <c r="J284" s="2" t="n"/>
     </row>
     <row r="285">
-      <c r="E285" s="5" t="n"/>
+      <c r="E285" s="2" t="n"/>
+      <c r="I285" s="2" t="n"/>
+      <c r="J285" s="2" t="n"/>
     </row>
     <row r="286">
-      <c r="E286" s="5" t="n"/>
+      <c r="E286" s="2" t="n"/>
+      <c r="I286" s="2" t="n"/>
+      <c r="J286" s="2" t="n"/>
     </row>
     <row r="287">
-      <c r="E287" s="5" t="n"/>
+      <c r="E287" s="2" t="n"/>
+      <c r="I287" s="2" t="n"/>
+      <c r="J287" s="2" t="n"/>
     </row>
     <row r="288">
-      <c r="E288" s="5" t="n"/>
+      <c r="E288" s="2" t="n"/>
+      <c r="I288" s="2" t="n"/>
+      <c r="J288" s="2" t="n"/>
     </row>
     <row r="289">
-      <c r="E289" s="5" t="n"/>
+      <c r="E289" s="2" t="n"/>
+      <c r="I289" s="2" t="n"/>
+      <c r="J289" s="2" t="n"/>
     </row>
     <row r="290">
-      <c r="E290" s="5" t="n"/>
+      <c r="E290" s="2" t="n"/>
+      <c r="I290" s="2" t="n"/>
+      <c r="J290" s="2" t="n"/>
     </row>
     <row r="291">
-      <c r="E291" s="5" t="n"/>
+      <c r="E291" s="2" t="n"/>
+      <c r="I291" s="2" t="n"/>
+      <c r="J291" s="2" t="n"/>
     </row>
     <row r="292">
-      <c r="E292" s="5" t="n"/>
+      <c r="E292" s="2" t="n"/>
+      <c r="I292" s="2" t="n"/>
+      <c r="J292" s="2" t="n"/>
     </row>
     <row r="293">
-      <c r="E293" s="5" t="n"/>
+      <c r="E293" s="2" t="n"/>
+      <c r="I293" s="2" t="n"/>
+      <c r="J293" s="2" t="n"/>
     </row>
     <row r="294">
-      <c r="E294" s="5" t="n"/>
+      <c r="E294" s="2" t="n"/>
+      <c r="I294" s="2" t="n"/>
+      <c r="J294" s="2" t="n"/>
     </row>
     <row r="295">
-      <c r="E295" s="5" t="n"/>
+      <c r="E295" s="2" t="n"/>
+      <c r="I295" s="2" t="n"/>
+      <c r="J295" s="2" t="n"/>
     </row>
     <row r="296">
-      <c r="E296" s="5" t="n"/>
+      <c r="E296" s="2" t="n"/>
+      <c r="I296" s="2" t="n"/>
+      <c r="J296" s="2" t="n"/>
     </row>
     <row r="297">
-      <c r="E297" s="5" t="n"/>
+      <c r="E297" s="2" t="n"/>
+      <c r="I297" s="2" t="n"/>
+      <c r="J297" s="2" t="n"/>
     </row>
     <row r="298">
-      <c r="E298" s="5" t="n"/>
+      <c r="E298" s="2" t="n"/>
+      <c r="I298" s="2" t="n"/>
+      <c r="J298" s="2" t="n"/>
     </row>
     <row r="299">
-      <c r="E299" s="5" t="n"/>
+      <c r="E299" s="2" t="n"/>
+      <c r="I299" s="2" t="n"/>
+      <c r="J299" s="2" t="n"/>
     </row>
     <row r="300">
-      <c r="E300" s="5" t="n"/>
+      <c r="E300" s="2" t="n"/>
+      <c r="I300" s="2" t="n"/>
+      <c r="J300" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="직분" error="목록에서 골라 주세요" type="list">
       <formula1>"성도,집사,권사,안수집사,장로,전도사,목사,사모,학생"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="상태" error="임명·취소·신청 중에 골라 주세요 (비우면 임명)" type="list">
+      <formula1>"임명,취소,신청"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1553,7 +2052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1561,246 +2060,346 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr"/>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr"/>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>2027 사역명단 올리기 — 적는 법</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
-      <c r="B2" s="8" t="inlineStr"/>
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>어디에 쓰나</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>gocheok.onlybible.kr → 설정 → 관리 페이지 → 사역관리 → 「종이 명단 올리기」</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>어떻게</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>「명단」 시트에서 적은 칸을 통째로 복사해(Ctrl+C) 화면의 큰 칸에 붙여넣기(Ctrl+V)</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>이 파일을 그대로 올리거나(「📂 엑셀 파일 올리기」), 「명단」 시트의 칸을 복사해 붙여넣습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>「붙여넣은 것 살펴보기」를 누르면 줄마다 판정이 나옵니다. 고칠 것이 없으면 「명단 넣기」.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>⚠️ 가장 중요</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>교구·목장·이름은 앱 로그인과 똑같이 — 한 글자만 달라도 다른 분이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>앱에 없는 분이면 계정을 새로 만듭니다. 나중에 그분이 앱에 로그인하면 이 명단이 그대로 보입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>종이는 이미 정해진 명단이라 화면에서 「임명」으로 넣는 것이 기본입니다.</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>줄마다 「임명·취소·신청」으로 적습니다. 비우면 임명으로 들어갑니다(종이는 정해진 명단이니까).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>「취소」로 넣으려면 사유를 함께 적어 주세요(관리자만 봅니다).</t>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>「취소」로 적은 줄은 사유도 함께 적어 주세요(관리자만 봅니다).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>신청일·임명일은 2026-12-15 꼴로. 비우면 올린 날로 들어갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>겹칠 때</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>앱으로 이미 낸 신청과 겹치면 새로 넣지 않고 그 건의 상태만 바꿉니다.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>이미 같은 상태인 줄은 손대지 않습니다 — 같은 명단을 두 번 올려도 안전합니다.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>올릴 때는 앱 알림이 가지 않습니다. 알림이 필요하면 현황 화면에서 한 분씩 눌러 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>한 번에</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>300줄까지. 더 많으면 나누어 올려 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>칸 설명</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>교구</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>앱 로그인과 똑같이 (믿음·소망·사랑·섬김·은혜·화평·기쁨·새가족)   예) 화평</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>목장</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>숫자만 적어도 됩니다 (20 = 20목장)   예) 20</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>앱 로그인과 똑같이 — 한 글자만 달라도 다른 분이 됩니다   예) 홍길동</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>직분</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>성도·집사·권사·안수집사·장로·전도사·목사·사모·학생   예) 안수집사</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>휴대폰</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>본인 확인·중복 찾기에 씁니다 (임명·취소로 넣으면 저장 뒤 지워집니다)   예) 010-1234-5678</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>사역팀</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>사역 목록에 있는 이름 그대로   예) 신앙운동</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>위원회(선택)</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>같은 이름의 사역팀이 둘 이상일 때만 적어 주세요   예) 제자양육부</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>하위 선택(선택)</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>「어와나 택1」처럼 고르는 것이 있을 때만</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>신청일(선택)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>비우면 올린 날로 들어갑니다   예) 2026-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>임명일(선택)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>임명·취소로 넣을 때 그 날짜 — 비우면 올린 날   예) 2026-12-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>상태(선택)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>임명·취소·신청 중 하나. 비우면 임명으로 들어갑니다   예) 임명</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>사유(취소일 때)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>취소로 적은 줄만 — 관리자만 봅니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>교구 / 목장 / 이름 / 직분 / 휴대폰 / 사역팀 / 위원회(선택) / 하위 선택(선택) / 신청일(선택) / 임명일(선택) / 상태(선택) / 사유(취소일 때)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>화평 / 20 / 홍길동 / 집사 / 010-1234-5678 / 신앙운동 / 제자양육부 / - / 2026-12-15 / 2026-12-27 / 임명 / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>사랑 / 3 / 홍길동 / 권사 / 010-2345-6789 / 방송실 운영 / 방송전산부 / - / 2026-12-15 / - / - / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>믿음 / 7 / 홍길동 / 집사 / 010-3456-7890 / 운영 / 새가족부 / - / - / 2026-12-27 / 취소 / 부서 요청으로 취소</t>
         </is>
       </c>
     </row>

--- a/ministry/2027_사역명단_올리기_양식.xlsx
+++ b/ministry/2027_사역명단_올리기_양식.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>위원회(선택)</t>
+          <t>부서(선택)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2294,7 +2294,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>위원회(선택)</t>
+          <t>부서(선택)</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>교구 / 목장 / 이름 / 직분 / 휴대폰 / 사역팀 / 위원회(선택) / 하위 선택(선택) / 신청일(선택) / 임명일(선택) / 상태(선택) / 사유(취소일 때)</t>
+          <t>교구 / 목장 / 이름 / 직분 / 휴대폰 / 사역팀 / 부서(선택) / 하위 선택(선택) / 신청일(선택) / 임명일(선택) / 상태(선택) / 사유(취소일 때)</t>
         </is>
       </c>
     </row>
